--- a/hospitality_forms/014_hospitality_application_form--hospitality_forms.xlsx
+++ b/hospitality_forms/014_hospitality_application_form--hospitality_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1007,8 +1007,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'hospitality'}</t>
+          <t>hospitality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'hospitality'}</t>
+          <t>hospitality</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'food_service'}</t>
+          <t>food_service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'food_service'}</t>
+          <t>food service</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'customer_service'}</t>
+          <t>customer service</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'coworker'}</t>
+          <t>coworker</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'coworker'}</t>
+          <t>coworker</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'assistant_manager'}</t>
+          <t>assistant_manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'assistant_manager'}</t>
+          <t>assistant manager</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'under_reviewæk'}</t>
+          <t>under_reviewæk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'under_reviewæk'}</t>
+          <t>under reviewæk</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'interview'}</t>
+          <t>interview</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'interview'}</t>
+          <t>interview</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'underประก'}</t>
+          <t>underประก</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'underประก'}</t>
+          <t>underประก</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'selected_for_interview'}</t>
+          <t>selected_for_interview</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'selected_for_interview'}</t>
+          <t>selected for interview</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'under_processing'}</t>
+          <t>under_processing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'under_processing'}</t>
+          <t>under processing</t>
         </is>
       </c>
     </row>
